--- a/daily_matches/job_matches_2026-07-16.xlsx
+++ b/daily_matches/job_matches_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S3, EC2, Redshift, Data Lake, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b22cbf19f8a0047</t>
+          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, Apache Airflow, Git, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01844276a565bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=937091ef92a9caaa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Clinical Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Baylor Scott &amp; White Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, Keras, CI/CD, Git, Snowflake, PySpark, Python</t>
+          <t>Generative AI, RAG, Copilot, CI/CD, Git, Cassandra, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce2f82acc4bd9b84</t>
+          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>QA Automation Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Reputation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Glue, Terraform, Git, PySpark, Kafka, PostgreSQL, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bcb623acf634f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=f5e6265ced15847f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer II - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>RAG, S3, Glue, Redshift, Terraform, Databricks, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d6990f289514b78</t>
+          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Batchelor &amp; Kimball</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Conyers, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>RAG, Glue, Kubernetes, CI/CD, Terraform, Databricks, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist ll - Digital Intelligence</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Git, Databricks, PySpark, Python, SQL</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30cd659014977d39</t>
+          <t>https://www.indeed.com/viewjob?jk=e30419cda8d1db5a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist ll - Digital Intelligence</t>
+          <t>Software Engineer II - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Git, Databricks, PySpark, Python, SQL</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3334cfabcc288667</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4a46b9a6c0e288</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist ll - Digital Intelligence</t>
+          <t>Software Engineer- Backend</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Git, Databricks, PySpark, Python, SQL</t>
+          <t>RAG, CI/CD, Git, Kafka, Cassandra, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83c437377562639</t>
+          <t>https://www.indeed.com/viewjob?jk=08085382ebf80b3e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist ll - Digital Intelligence</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Git, Databricks, PySpark, Python, SQL</t>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, Snowflake, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,147 +811,77 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9f33c2355657898</t>
+          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist ll - Digital Intelligence</t>
+          <t>Data Scientist (Insurance Product)-Senior Associate</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Git, Databricks, PySpark, Python, SQL</t>
+          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959a200a7efdad30</t>
+          <t>https://www.indeed.com/viewjob?jk=5f70b2d2bc05e580</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate AI/ML Engineer</t>
+          <t>Data Engineer - Finance Technology Solutions</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, PySpark, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8d85951c8d864fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=937834d85c864245</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Software Engineer Professional</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Freddie Mac</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Snowflake, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d37ab46efd6c76</t>
+          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-16.xlsx
+++ b/daily_matches/job_matches_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>AI Software Engineer (GenAI/RAG/Azure AI Foundry) - REMOTE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Phia Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Pinecone, Prompt Engineering, Azure ML, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
+          <t>https://www.indeed.com/viewjob?jk=c9f821eb0bdcab14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, Apache Airflow, Git, Snowflake, Databricks, PySpark</t>
+          <t>AI Engineer, RAG, Redshift, BigQuery, Synapse, Dataflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=937091ef92a9caaa</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeade119569bbf7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, Cassandra, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Redshift, BigQuery, Synapse, Dataflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
+          <t>https://www.indeed.com/viewjob?jk=93edda5c98f4cdb4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reputation</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+          <t>AI Engineer, RAG, Redshift, BigQuery, Synapse, Dataflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5e6265ced15847f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1cdcb324b377bf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer II - Big Data &amp; AWS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Terraform, Databricks, Redshift, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Redshift, BigQuery, Synapse, Dataflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
+          <t>https://www.indeed.com/viewjob?jk=06bc1107dcef567b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Glue, Kubernetes, CI/CD, Terraform, Databricks, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Redshift, BigQuery, Synapse, Dataflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab6ea52221dfe</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, SQL, R, Java</t>
+          <t>AI Engineer, RAG, Redshift, BigQuery, Synapse, Dataflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30419cda8d1db5a</t>
+          <t>https://www.indeed.com/viewjob?jk=5b1bb8e723d49656</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer II - Full Stack Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tripledot Studios</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, SQL, R, Java</t>
+          <t>Machine Learning Engineer, Generative AI, Copilot, MLflow, Docker, Kubernetes, CI/CD, Git, Matplotlib, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,94 +741,94 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4a46b9a6c0e288</t>
+          <t>https://www.indeed.com/viewjob?jk=01f18195cabddde2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer- Backend</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>STORD Warehouse</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Kafka, Cassandra, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, BigQuery, Data Lake, Apache Airflow, Git, Snowflake, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08085382ebf80b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=f9eba76ae08417b0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Engineer, AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, CI/CD, Snowflake, Databricks, PySpark, Python, SQL, R</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Terraform, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=bfa036e692a5d7ad</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist (Insurance Product)-Senior Associate</t>
+          <t>Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
+          <t>RAG, S3, Redshift, Data Lake, Kubernetes, Git, Databricks, Redshift, R, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f70b2d2bc05e580</t>
+          <t>https://www.indeed.com/viewjob?jk=91a702b31b4423d5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance Technology Solutions</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Visto360 AI Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,227 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, PySpark, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>TensorFlow, PyTorch, OpenCV, YOLO, Docker, Kubernetes, Git, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a76a330d999f6f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Visto360 AI Inc.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ann Arbor, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, OpenCV, YOLO, Docker, Kubernetes, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df403db341133e81</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Synapse, Git, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2174bb0a9426a2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Research Analyst</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Serco</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72324a634a6aa339</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Analytics and Research Analyst</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Serco</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ed87f1b68d00106</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Research Analyst</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Serco</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92570c91dc4631f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior AI Scientist</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Edward Jones</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=057b8b1de26bd487</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-16.xlsx
+++ b/daily_matches/job_matches_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Software Engineer (GenAI/RAG/Azure AI Foundry) - REMOTE</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Phia Group</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Pinecone, Prompt Engineering, Azure ML, FastAPI, Docker</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, S3, Glue, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9f821eb0bdcab14</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3a80ab86734aea</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Redshift, BigQuery, Synapse, Dataflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
+          <t>Data Scientist, LangChain, Mistral, TensorFlow, PyTorch, Azure ML, MLflow, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeade119569bbf7</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac351039409cb17</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Solutions Architect - Airflow (East Coast)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Philadelphia, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Redshift, BigQuery, Synapse, Dataflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
+          <t>Redshift, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93edda5c98f4cdb4</t>
+          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Hadoop/Spark/OCP/Big Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Redshift, BigQuery, Synapse, Dataflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
+          <t>RAG, S3, Data Lake, Docker, Kubernetes, CI/CD, Jenkins, Git, Hadoop, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1cdcb324b377bf</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa14baaf9fd7957</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>Learn Beyond Consulting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Redshift, BigQuery, Synapse, Dataflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
+          <t>BigQuery, CI/CD, Git, BigQuery, Kafka, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bc1107dcef567b</t>
+          <t>https://www.indeed.com/viewjob?jk=75af597329b51c24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer for Asset Management</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>Virginia Passenger Rail Authority</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Redshift, BigQuery, Synapse, Dataflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
+          <t>RAG, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab6ea52221dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=d66ccfdf783d3c46</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Business Intelligence Engineer - Digital Experiences &amp; Capabilities</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Redshift, BigQuery, Synapse, Dataflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
+          <t>RAG, Git, Hadoop, Tableau, Power BI, R, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b1bb8e723d49656</t>
+          <t>https://www.indeed.com/viewjob?jk=396f84d52464c1b4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Sr. Software Engineer, Marine &amp; RVC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tripledot Studios</t>
+          <t>Storable</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, Copilot, MLflow, Docker, Kubernetes, CI/CD, Git, Matplotlib, Python</t>
+          <t>RAG, Copilot, CI/CD, Git, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,19 +741,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01f18195cabddde2</t>
+          <t>https://www.indeed.com/viewjob?jk=c40ad6f4ade01528</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Quality Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>STORD Warehouse</t>
+          <t>Storable</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -762,46 +762,46 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Data Lake, Apache Airflow, Git, Snowflake, BigQuery, Python, SQL</t>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9eba76ae08417b0</t>
+          <t>https://www.indeed.com/viewjob?jk=fea99601a50a7b7b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Engineer, AI</t>
+          <t>Senior .Net Engineer - Real Time Product Engineering</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Terraform, Git, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfa036e692a5d7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=392f15a659f89a75</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Engineer, Data &amp; Analytics</t>
+          <t>Sr. QA Automation Engineer - Brokerage / Financial Services Domain (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Data Lake, Kubernetes, Git, Databricks, Redshift, R, Optimization</t>
+          <t>RAG, S3, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,252 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91a702b31b4423d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Visto360 AI Inc.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ann Arbor, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, OpenCV, YOLO, Docker, Kubernetes, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a76a330d999f6f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Visto360 AI Inc.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ann Arbor, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, OpenCV, YOLO, Docker, Kubernetes, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df403db341133e81</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Data QA</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Synapse, Git, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2174bb0a9426a2a</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72324a634a6aa339</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ed87f1b68d00106</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92570c91dc4631f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Senior AI Scientist</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=057b8b1de26bd487</t>
+          <t>https://www.indeed.com/viewjob?jk=62912356a020a29b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-16.xlsx
+++ b/daily_matches/job_matches_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Excel Sports Management</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, S3, Glue, Docker</t>
+          <t>Generative AI, S3, Glue, Athena, Redshift, Data Lake, FastAPI, Docker, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3a80ab86734aea</t>
+          <t>https://www.indeed.com/viewjob?jk=54c48dbd46696795</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IT Data Scientist</t>
+          <t>Devops – Azure</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>DISTILLERY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, Mistral, TensorFlow, PyTorch, Azure ML, MLflow, Docker, Kubernetes, Git</t>
+          <t>RAG, Redshift, Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac351039409cb17</t>
+          <t>https://www.indeed.com/viewjob?jk=eb316c4d0d8d4a0b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (East Coast)</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, XGBoost, Snowflake, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9e031e7f145bb8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Hadoop/Spark/OCP/Big Data</t>
+          <t>Artificial Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, Docker, Kubernetes, CI/CD, Jenkins, Git, Hadoop, SQL</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Redshift, Synapse, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa14baaf9fd7957</t>
+          <t>https://www.indeed.com/viewjob?jk=d1b59a24505be799</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Learn Beyond Consulting</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BigQuery, CI/CD, Git, BigQuery, Kafka, Hadoop, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, Apache Airflow, CI/CD, Git, PostgreSQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75af597329b51c24</t>
+          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer for Asset Management</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Virginia Passenger Rail Authority</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Hopkinton, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, Apache Airflow, CI/CD, Git, PostgreSQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66ccfdf783d3c46</t>
+          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer - Digital Experiences &amp; Capabilities</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Git, Hadoop, Tableau, Power BI, R, Scala, Optimization, A/B Testing</t>
+          <t>Generative AI, RAG, Gemini, EC2, CI/CD, Terraform, Git, Snowflake, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,49 +706,49 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396f84d52464c1b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Marine &amp; RVC</t>
+          <t>Software Engineering, Sr Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Storable</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, MySQL, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40ad6f4ade01528</t>
+          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Quality Engineer</t>
+          <t>Software Engineer II, RVC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Copilot, CI/CD, Git, MySQL, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea99601a50a7b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=13fae56d36358ceb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior .Net Engineer - Real Time Product Engineering</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Git, Python, SQL, R, Scala</t>
+          <t>Data Scientist, XGBoost, NLTK, MLflow, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=392f15a659f89a75</t>
+          <t>https://www.indeed.com/viewjob?jk=815c171b148304d3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. QA Automation Engineer - Brokerage / Financial Services Domain (FTE / Hybrid)</t>
+          <t>Senior Software Engineer - Agent Development</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,297 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62912356a020a29b</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad0b5ce20d52d31</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CODE PLUS INC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, MLflow, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=459b88eaeb592e14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CODE PLUS INC</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, MLflow, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89493a55f653643d</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CODE PLUS INC</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Fairfax, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, MLflow, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cd747fe6299f2ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Machine Learning Research Engineer – Embodied AI &amp; Robot Learning</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Lens Technology Inc.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, OpenCV, Docker, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2ebf28109df809f</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dauntless</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57ad2c5a4546524a</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Analytics and Research Analyst</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Serco</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7408d64534cf3d1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics and Research Analyst</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Serco</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=205f73efd4f5254c</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Brookfield Properties</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Charleston, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08f901faf9b58b9f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-16.xlsx
+++ b/daily_matches/job_matches_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI DevOps Engineer (Global)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Excel Sports Management</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, S3, Glue, Athena, Redshift, Data Lake, FastAPI, Docker, Apache Airflow, CI/CD</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, MLflow, Docker, Kubernetes, Apache Airflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c48dbd46696795</t>
+          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Devops – Azure</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DISTILLERY</t>
+          <t>Everpure</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Snowflake</t>
+          <t>RAG, Pinecone, Prompt Engineering, S3, EC2, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb316c4d0d8d4a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=b86139110d78b678</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, XGBoost, Snowflake, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9e031e7f145bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer III</t>
+          <t>AI &amp; Automation Developer - Remote - Sarnova</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Sarnova HC, LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Redshift, Synapse, Snowflake, Databricks, Redshift</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1b59a24505be799</t>
+          <t>https://www.indeed.com/viewjob?jk=e617c34efa7ce23c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>AI &amp; Automation Developer - Remote - Sarnova</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Sarnova HC, LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, Apache Airflow, CI/CD, Git, PostgreSQL, Power BI, Python</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd88c025e50ad47</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Customer Deployment Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hopkinton, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, Apache Airflow, CI/CD, Git, PostgreSQL, Power BI, Python</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
+          <t>https://www.indeed.com/viewjob?jk=d91a006319608065</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Grafana Engineer</t>
+          <t>Customer Deployment Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, EC2, CI/CD, Terraform, Git, Snowflake, Python, R</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
+          <t>https://www.indeed.com/viewjob?jk=4627ac16a4699ddb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineering, Sr Engineer</t>
+          <t>Infrastructure Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>University of Florida</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Gainesville, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, LLaMA, Gemini, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
+          <t>https://www.indeed.com/viewjob?jk=b871980195f62ca1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer II, RVC</t>
+          <t>Technical Solutions Engineer - Pre</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Storable</t>
+          <t>Verily</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, MySQL, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, BigQuery, Terraform, Git, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13fae56d36358ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, XGBoost, NLTK, MLflow, Databricks, PySpark, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Gemini, EC2, CI/CD, Terraform, Git, Snowflake, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815c171b148304d3</t>
+          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Agent Development</t>
+          <t>AI Modeling Specialist Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, Git, Python, R, Java, Scala</t>
+          <t>RAG, LLaMA, Mistral, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad0b5ce20d52d31</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad90233c0c43296</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Software Engineer, Test Infrastructure (C/C++)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CODE PLUS INC</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hawthorne, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, MLflow, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, PostgreSQL, Python, SQL, R, Java, C++, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459b88eaeb592e14</t>
+          <t>https://www.indeed.com/viewjob?jk=3228e79afcdd35ed</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>COE QE DevOps role - C1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CODE PLUS INC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, MLflow, Databricks, Python, SQL, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89493a55f653643d</t>
+          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CODE PLUS INC</t>
+          <t>MassMutual</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Springfield, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, MLflow, Databricks, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Python, SQL, R, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd747fe6299f2ce</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7f8d8f127c909b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Machine Learning Research Engineer – Embodied AI &amp; Robot Learning</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lens Technology Inc.</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, TensorFlow, PyTorch, OpenCV, Docker, Git, Python, R</t>
+          <t>RAG, S3, EC2, CI/CD, Terraform, Git, Databricks, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,147 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ebf28109df809f</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Dauntless</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57ad2c5a4546524a</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7408d64534cf3d1f</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Senior Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=205f73efd4f5254c</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Brookfield Properties</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Charleston, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08f901faf9b58b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=daf8df291fafa8fc</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-16.xlsx
+++ b/daily_matches/job_matches_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer (Global)</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, MLflow, Docker, Kubernetes, Apache Airflow, CI/CD, GitHub Actions</t>
+          <t>RAG, S3, Redshift, BigQuery, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
+          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Machine Learning - AI Engineer (Remote)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Everpure</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Pinecone, Prompt Engineering, S3, EC2, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Gemini, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86139110d78b678</t>
+          <t>https://www.indeed.com/viewjob?jk=ce577ef97b7d087b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>STORD Warehouse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, MySQL</t>
+          <t>Glue, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
+          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI &amp; Automation Developer - Remote - Sarnova</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sarnova HC, LLC</t>
+          <t>Enterprise Knowledge</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Power BI, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Docker, CI/CD, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e617c34efa7ce23c</t>
+          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI &amp; Automation Developer - Remote - Sarnova</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sarnova HC, LLC</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reno, NV, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Power BI, Python, SQL</t>
+          <t>Data Scientist, RAG, Data Lake, MLflow, Apache Airflow, CI/CD, Git, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd88c025e50ad47</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Customer Deployment Engineer</t>
+          <t>Senior Data &amp; Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>AKUVO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI, Python</t>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, LightGBM, Synapse, MLflow, CI/CD, Databricks, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d91a006319608065</t>
+          <t>https://www.indeed.com/viewjob?jk=2f806492df362e0b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Customer Deployment Engineer</t>
+          <t>Cloud Solution Architect (Remote)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI, Python</t>
+          <t>Generative AI, RAG, Copilot, Cortex, S3, EC2, Data Lake, CI/CD, Snowflake, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4627ac16a4699ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Infrastructure Platform Engineer</t>
+          <t>Mid Backend Engineer (Java / Python)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Nexaminds</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gainesville, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, LLaMA, Gemini, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b871980195f62ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0e192d31c0c09d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Technical Solutions Engineer - Pre</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Verily</t>
+          <t>DaVita</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Terraform, Git, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d067fbdca938376c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Grafana Engineer</t>
+          <t>Sr. Analytics Engineer (Remote)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Rula</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, EC2, CI/CD, Terraform, Git, Snowflake, Python, R</t>
+          <t>RAG, Copilot, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdf357ae0696a3c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Modeling Specialist Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Parafin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Mistral, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
+          <t>RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad90233c0c43296</t>
+          <t>https://www.indeed.com/viewjob?jk=e76a0ef4b6f79f26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer, Test Infrastructure (C/C++)</t>
+          <t>Software Engineer - Limited Tenure - Hybrid</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hawthorne, CA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, PostgreSQL, Python, SQL, R, Java, C++, Scala</t>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3228e79afcdd35ed</t>
+          <t>https://www.indeed.com/viewjob?jk=5da6426fcae84c0b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COE QE DevOps role - C1</t>
+          <t>Project Controls, Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>RAG, AWS SageMaker, Azure ML, PostgreSQL, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f66e61d041240a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Project Controls, Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MassMutual</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Python, SQL, R, Optimization, Bayesian</t>
+          <t>RAG, AWS SageMaker, Azure ML, PostgreSQL, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,42 +951,427 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7f8d8f127c909b</t>
+          <t>https://www.indeed.com/viewjob?jk=df8062c19c4d1d41</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Software Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7cbf90cc7bf6fe09</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Securiport</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4acfc843a70eb04e</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Agentic AI Developer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Calpion/Plutus Health</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52123942ff86403d</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Defense Unicorns</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Defense Unicorns</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Front End Developer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>10</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, CI/CD, Terraform, Git, Databricks, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=daf8df291fafa8fc</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, CI/CD, Git, Kafka, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b7d8f3ccba40eec</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GenAI Architect – AI Assurance &amp; Quality Engineering</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c8e9e2c5ab072af</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Platform Support Architect</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DDN</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Pinecone, Docker, Kubernetes, CI/CD, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bc1680d898037bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sr BI Platform Administrator</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dynatrace</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Copilot, Cortex, CI/CD, Git, Snowflake, Power BI, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86ea8496bfe4cd07</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Quality Engineer - 770</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Quantinuum</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Broomfield, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3768d749eed916f</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, PySpark, Hadoop, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8f8cff293c21f28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Jr Developer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b43ffdf37ac6cf95</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-16.xlsx
+++ b/daily_matches/job_matches_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Senior Consultant - AI/ML</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sugar Land, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, BigQuery, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
+          <t>TensorFlow, PyTorch, XGBoost, AWS SageMaker, S3, Glue, Redshift, Data Lake, CI/CD, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
+          <t>https://www.indeed.com/viewjob?jk=65b8240c3efb30fa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Machine Learning - AI Engineer (Remote)</t>
+          <t>Software Engineer/Full Stack Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, Gemini, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, MongoDB, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce577ef97b7d087b</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf986da2977e0aa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>STORD Warehouse</t>
+          <t>Build-A-Bear Workshop</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Glue, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, Python</t>
+          <t>RAG, Synapse, Data Lake, CI/CD, Git, Databricks, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Enterprise Knowledge</t>
+          <t>Resmed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Docker, CI/CD, GitHub Actions, Git, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
+          <t>https://www.indeed.com/viewjob?jk=756b0e8f5fece0a0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Platform Engineer - Digital Workforce and BI Tools</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Reno, NV, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, MLflow, Apache Airflow, CI/CD, Git, Databricks, PySpark, Python</t>
+          <t>RAG, Copilot, Synapse, AKS, Git, Snowflake, Databricks, Power BI, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
+          <t>https://www.indeed.com/viewjob?jk=31fc8fcfb85ba7b0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Machine Learning Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AKUVO</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, LightGBM, Synapse, MLflow, CI/CD, Databricks, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f806492df362e0b</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba2d09365f6ee5a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect (Remote)</t>
+          <t>Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Cortex, S3, EC2, Data Lake, CI/CD, Snowflake, R</t>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
+          <t>https://www.indeed.com/viewjob?jk=6c0fcfa492c90666</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mid Backend Engineer (Java / Python)</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nexaminds</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R</t>
+          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0e192d31c0c09d</t>
+          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Associate Application Engineer (HYBRID TO MA)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DaVita</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d067fbdca938376c</t>
+          <t>https://www.indeed.com/viewjob?jk=2998583d8b441f38</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer (Remote)</t>
+          <t>Software Engineer III, Site Reliability</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rula</t>
+          <t>MyFitnessPal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL</t>
+          <t>Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,567 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdf357ae0696a3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Data Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Parafin</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e76a0ef4b6f79f26</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Software Engineer - Limited Tenure - Hybrid</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Mayo Clinic</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Rochester, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5da6426fcae84c0b</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Project Controls, Database Administrator (DBA)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, AWS SageMaker, Azure ML, PostgreSQL, Tableau, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f66e61d041240a</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Project Controls, Database Administrator (DBA)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Columbia, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, AWS SageMaker, Azure ML, PostgreSQL, Tableau, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df8062c19c4d1d41</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Sr Software Developer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Charles Schwab</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Southlake, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Prompt Engineering, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7cbf90cc7bf6fe09</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Securiport</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4acfc843a70eb04e</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Agentic AI Developer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Calpion/Plutus Health</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52123942ff86403d</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Defense Unicorns</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Defense Unicorns</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Front End Developer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, S3, CI/CD, Git, Kafka, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b7d8f3ccba40eec</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>GenAI Architect – AI Assurance &amp; Quality Engineering</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8e9e2c5ab072af</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Platform Support Architect</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>DDN</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Pinecone, Docker, Kubernetes, CI/CD, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc1680d898037bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Sr BI Platform Administrator</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Dynatrace</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Copilot, Cortex, CI/CD, Git, Snowflake, Power BI, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86ea8496bfe4cd07</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Software Quality Engineer - 770</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Quantinuum</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Broomfield, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3768d749eed916f</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Adyen</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, PySpark, Hadoop, Python, SQL, R, Scala, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f8cff293c21f28</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Jr Developer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Intone Networks</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b43ffdf37ac6cf95</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc6795cef576f9b</t>
         </is>
       </c>
     </row>
